--- a/output/StructureDefinition-BRAmostraBiologica-1.0.xlsx
+++ b/output/StructureDefinition-BRAmostraBiologica-1.0.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="461">
   <si>
     <t>Property</t>
   </si>
@@ -1118,6 +1118,10 @@
   </si>
   <si>
     <t>The quantity of specimen collected; for instance the volume of a blood sample, or the physical measurement of an anatomic pathology sample.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role[classCode=SPEC].player.quantity</t>
@@ -6772,24 +6776,24 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>95</v>
+        <v>356</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6815,10 +6819,10 @@
         <v>170</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6845,13 +6849,13 @@
         <v>76</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>76</v>
@@ -6869,7 +6873,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6884,21 +6888,21 @@
         <v>95</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6924,13 +6928,13 @@
         <v>170</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6956,13 +6960,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6980,7 +6984,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6995,21 +6999,21 @@
         <v>95</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7032,19 +7036,19 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7072,10 +7076,10 @@
         <v>175</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -7093,7 +7097,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7114,15 +7118,15 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7148,10 +7152,10 @@
         <v>322</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7202,7 +7206,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7217,7 +7221,7 @@
         <v>95</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
@@ -7228,10 +7232,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7337,10 +7341,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7448,10 +7452,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7561,10 +7565,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7590,10 +7594,10 @@
         <v>148</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7644,7 +7648,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7659,7 +7663,7 @@
         <v>95</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7670,10 +7674,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7699,10 +7703,10 @@
         <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7729,13 +7733,13 @@
         <v>76</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>76</v>
@@ -7753,7 +7757,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7779,10 +7783,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7805,13 +7809,13 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7862,7 +7866,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7877,21 +7881,21 @@
         <v>95</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7917,10 +7921,10 @@
         <v>342</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7971,7 +7975,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -7997,10 +8001,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8026,10 +8030,10 @@
         <v>322</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8080,7 +8084,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8095,7 +8099,7 @@
         <v>95</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -8106,10 +8110,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8215,10 +8219,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8326,10 +8330,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8439,10 +8443,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8468,10 +8472,10 @@
         <v>141</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8522,7 +8526,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8543,15 +8547,15 @@
         <v>76</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8577,10 +8581,10 @@
         <v>148</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8631,7 +8635,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8646,7 +8650,7 @@
         <v>95</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8657,10 +8661,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8686,10 +8690,10 @@
         <v>170</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8716,13 +8720,13 @@
         <v>76</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>76</v>
@@ -8740,7 +8744,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8761,15 +8765,15 @@
         <v>76</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8795,10 +8799,10 @@
         <v>353</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8849,7 +8853,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8861,24 +8865,24 @@
         <v>76</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>95</v>
+        <v>356</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8904,10 +8908,10 @@
         <v>353</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8958,7 +8962,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -8970,24 +8974,24 @@
         <v>76</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>95</v>
+        <v>356</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9010,13 +9014,13 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9043,13 +9047,13 @@
         <v>76</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>76</v>
@@ -9067,7 +9071,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9082,21 +9086,21 @@
         <v>95</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9122,16 +9126,16 @@
         <v>170</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>76</v>
@@ -9159,10 +9163,10 @@
         <v>175</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>76</v>
@@ -9180,7 +9184,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9201,15 +9205,15 @@
         <v>76</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9232,13 +9236,13 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9289,7 +9293,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9304,13 +9308,13 @@
         <v>95</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
